--- a/construction_template/data/templates_blank/defect_control.xlsx
+++ b/construction_template/data/templates_blank/defect_control.xlsx
@@ -72,7 +72,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>任泰技術顧問有限公司</t>
+    <t xml:space="preserve"/>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>

--- a/construction_template/data/templates_blank/defect_control.xlsx
+++ b/construction_template/data/templates_blank/defect_control.xlsx
@@ -72,7 +72,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>

--- a/construction_template/data/templates_blank/defect_control.xlsx
+++ b/construction_template/data/templates_blank/defect_control.xlsx
@@ -73,7 +73,6 @@
   </si>
   <si>
     <t/>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
